--- a/Warehouse.Infrastructure/Documents/Templates/GoodsIssuePermit.xlsx
+++ b/Warehouse.Infrastructure/Documents/Templates/GoodsIssuePermit.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pc1-qa\source\repos\warhouse-asin-main\Warehouse.Infrastructure\Documents\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D0C693-A7B7-43BB-9FD0-B931B1A619E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB287333-3878-4ED5-B674-36C7375C8760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="مجوز خروج کالا" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'مجوز خروج کالا'!$A$1:$J$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'مجوز خروج کالا'!$A$1:$J$20</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -27,8 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -101,20 +99,6 @@
   </si>
   <si>
     <t>خروج اقلام و کالاهای فوق توسط آقای ................................ با وسیله نقلیه/ بدون وسیله نقلیه به شماره شهربانی .......................... بلامانع است.</t>
-  </si>
-  <si>
-    <r>
-      <t>کد مستند:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="18"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>FN06</t>
-    </r>
   </si>
   <si>
     <r>
@@ -130,12 +114,26 @@
       <t>2</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>کد مستند:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>FN06</t>
+    </r>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -197,12 +195,6 @@
     </font>
     <font>
       <sz val="18"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <color rgb="FF00B0F0"/>
       <name val="B Nazanin"/>
       <charset val="178"/>
@@ -236,6 +228,18 @@
       <name val="B Nazanin"/>
       <charset val="178"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="B Nazanin"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -746,17 +750,62 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
@@ -767,6 +816,27 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -797,6 +867,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -824,6 +897,30 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
@@ -831,99 +928,6 @@
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -949,15 +953,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>144557</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>104776</xdr:rowOff>
+      <xdr:colOff>123825</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>496982</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>90208</xdr:rowOff>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>238125</xdr:rowOff>
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
@@ -971,9 +975,9 @@
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
-        <a:xfrm>
-          <a:off x="10149366830" y="104776"/>
-          <a:ext cx="804863" cy="985557"/>
+        <a:xfrm flipH="1">
+          <a:off x="9993401400" y="352425"/>
+          <a:ext cx="790575" cy="571500"/>
           <a:chOff x="0" y="0"/>
           <a:chExt cx="1510234" cy="1502183"/>
         </a:xfrm>
@@ -1368,7 +1372,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.7109375" customWidth="1"/>
@@ -1381,60 +1385,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="39"/>
+      <c r="C1" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="59" t="s">
-        <v>21</v>
-      </c>
-      <c r="J1" s="60"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="56" t="s">
+        <v>22</v>
+      </c>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="26"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="26"/>
-      <c r="G2" s="26"/>
-      <c r="H2" s="27"/>
-      <c r="I2" s="61" t="s">
+      <c r="A2" s="40"/>
+      <c r="B2" s="41"/>
+      <c r="C2" s="48"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="58" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="62"/>
+      <c r="J2" s="59"/>
     </row>
     <row r="3" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="25"/>
-      <c r="D3" s="26"/>
-      <c r="E3" s="26"/>
-      <c r="F3" s="26"/>
-      <c r="G3" s="26"/>
-      <c r="H3" s="27"/>
-      <c r="I3" s="63" t="s">
+      <c r="A3" s="40"/>
+      <c r="B3" s="41"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="49"/>
+      <c r="E3" s="49"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="50"/>
+      <c r="I3" s="54" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="64"/>
+      <c r="J3" s="55"/>
     </row>
     <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="18"/>
-      <c r="B4" s="19"/>
-      <c r="C4" s="25"/>
-      <c r="D4" s="26"/>
-      <c r="E4" s="26"/>
-      <c r="F4" s="26"/>
-      <c r="G4" s="26"/>
-      <c r="H4" s="27"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="41"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="50"/>
       <c r="I4" s="4" t="s">
         <v>12</v>
       </c>
@@ -1443,265 +1447,251 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="25.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="20"/>
-      <c r="B5" s="21"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29"/>
-      <c r="E5" s="29"/>
-      <c r="F5" s="29"/>
-      <c r="G5" s="29"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="35" t="s">
-        <v>22</v>
-      </c>
-      <c r="J5" s="34"/>
+      <c r="A5" s="42"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="51"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="53"/>
+      <c r="I5" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="5"/>
     </row>
     <row r="6" spans="1:10" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="36" t="s">
+      <c r="A6" s="44" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="37"/>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37" t="s">
+      <c r="B6" s="31"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="38"/>
-      <c r="J6" s="39"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="33"/>
     </row>
     <row r="7" spans="1:10" ht="38.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="13"/>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="15"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:10" ht="73.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="53" t="s">
+      <c r="A8" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="B8" s="54" t="s">
+      <c r="B8" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="55"/>
-      <c r="D8" s="56" t="s">
+      <c r="C8" s="14"/>
+      <c r="D8" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="56" t="s">
+      <c r="E8" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="56" t="s">
+      <c r="F8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="G8" s="56" t="s">
+      <c r="G8" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="H8" s="57" t="s">
+      <c r="H8" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="54"/>
-      <c r="J8" s="58"/>
+      <c r="I8" s="13"/>
+      <c r="J8" s="61"/>
     </row>
     <row r="9" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="47">
+      <c r="A9" s="7">
         <v>1</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="8"/>
+      <c r="B9" s="15"/>
+      <c r="C9" s="16"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
       <c r="G9" s="2"/>
-      <c r="H9" s="31"/>
-      <c r="I9" s="32"/>
-      <c r="J9" s="33"/>
+      <c r="H9" s="62"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="64"/>
     </row>
     <row r="10" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="48">
+      <c r="A10" s="8">
         <v>2</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="6"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
-      <c r="H10" s="9"/>
-      <c r="I10" s="10"/>
-      <c r="J10" s="11"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
     </row>
     <row r="11" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="48">
+      <c r="A11" s="8">
         <v>3</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="6"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="12"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
-      <c r="H11" s="9"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="11"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="26"/>
     </row>
     <row r="12" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="48">
+      <c r="A12" s="8">
         <v>4</v>
       </c>
-      <c r="B12" s="5"/>
-      <c r="C12" s="6"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="12"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
-      <c r="H12" s="9"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="11"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="26"/>
     </row>
     <row r="13" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="48">
+      <c r="A13" s="8">
         <v>5</v>
       </c>
-      <c r="B13" s="5"/>
-      <c r="C13" s="6"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="12"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
-      <c r="H13" s="9"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="11"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="26"/>
     </row>
     <row r="14" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="48">
+      <c r="A14" s="8">
         <v>6</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="6"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="12"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
-      <c r="H14" s="9"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="11"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="26"/>
     </row>
     <row r="15" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="48">
+      <c r="A15" s="8">
         <v>7</v>
       </c>
-      <c r="B15" s="5"/>
-      <c r="C15" s="6"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="12"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="9"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="11"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="26"/>
     </row>
     <row r="16" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="48">
+      <c r="A16" s="8">
         <v>8</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="6"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="9"/>
-      <c r="I16" s="10"/>
-      <c r="J16" s="11"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="26"/>
     </row>
     <row r="17" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="48">
+      <c r="A17" s="8">
         <v>9</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="6"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="12"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="9"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="11"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="26"/>
     </row>
     <row r="18" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="48">
+      <c r="A18" s="8">
         <v>10</v>
       </c>
-      <c r="B18" s="5"/>
-      <c r="C18" s="6"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="12"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="11"/>
-    </row>
-    <row r="19" spans="1:10" ht="99" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="48">
-        <v>11</v>
-      </c>
-      <c r="B19" s="5"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="9"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="11"/>
-    </row>
-    <row r="20" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="49" t="s">
+      <c r="H18" s="24"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="26"/>
+    </row>
+    <row r="19" spans="1:10" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="50"/>
-      <c r="I20" s="51"/>
-      <c r="J20" s="52"/>
-    </row>
-    <row r="21" spans="1:10" ht="107.25" customHeight="1" x14ac:dyDescent="0.85">
-      <c r="A21" s="40" t="s">
+      <c r="B19" s="28"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="30"/>
+    </row>
+    <row r="20" spans="1:10" ht="176.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="41"/>
-      <c r="C21" s="42"/>
-      <c r="D21" s="41" t="s">
+      <c r="B20" s="18"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="42"/>
-      <c r="F21" s="43" t="s">
+      <c r="E20" s="19"/>
+      <c r="F20" s="20" t="s">
         <v>17</v>
       </c>
-      <c r="G21" s="44"/>
-      <c r="H21" s="45"/>
-      <c r="I21" s="43" t="s">
+      <c r="G20" s="21"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="J21" s="46"/>
+      <c r="J20" s="23"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="35">
     <mergeCell ref="H8:J8"/>
     <mergeCell ref="H9:J9"/>
     <mergeCell ref="H10:J10"/>
@@ -1715,30 +1705,28 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="I1:J1"/>
     <mergeCell ref="I2:J2"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="I20:J20"/>
     <mergeCell ref="H13:J13"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="H15:J15"/>
     <mergeCell ref="H16:J16"/>
     <mergeCell ref="H17:J17"/>
     <mergeCell ref="H18:J18"/>
-    <mergeCell ref="H19:J19"/>
-    <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A19:J19"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B13:C13"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
     <mergeCell ref="B8:C8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B11:C11"/>
     <mergeCell ref="B12:C12"/>
-    <mergeCell ref="B13:C13"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
